--- a/数据表/Datas/FormatText_格式化文本.xlsx
+++ b/数据表/Datas/FormatText_格式化文本.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -105,6 +110,101 @@
   </si>
   <si>
     <t>{0} / {1}</t>
+  </si>
+  <si>
+    <t>RoundHUDRemainingTime</t>
+  </si>
+  <si>
+    <t>{0:00}:{1:00}</t>
+  </si>
+  <si>
+    <t>RoundHUDNorthLabel</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>RoundHUDFreeSlots</t>
+  </si>
+  <si>
+    <t>RoundHUDLootValue</t>
+  </si>
+  <si>
+    <t>{0:N0}</t>
+  </si>
+  <si>
+    <t>BackpackSafeCapacity</t>
+  </si>
+  <si>
+    <t>BackpackMemberHp</t>
+  </si>
+  <si>
+    <t>HP {0}/{1}</t>
+  </si>
+  <si>
+    <t>BackpackMemberMp</t>
+  </si>
+  <si>
+    <t>MP {0}/{1}</t>
+  </si>
+  <si>
+    <t>BackpackItemName</t>
+  </si>
+  <si>
+    <t>{0} x{1}</t>
+  </si>
+  <si>
+    <t>SettlementResult</t>
+  </si>
+  <si>
+    <t>{0}</t>
+  </si>
+  <si>
+    <t>SettlementTotalValue</t>
+  </si>
+  <si>
+    <t>SettlementElapsed</t>
+  </si>
+  <si>
+    <t>SettlementRedLootCount</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">{0} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>件</t>
+    </r>
+  </si>
+  <si>
+    <t>SettlementItemName</t>
+  </si>
+  <si>
+    <t>SettlementItemQuantity</t>
+  </si>
+  <si>
+    <t>×{0}</t>
+  </si>
+  <si>
+    <t>SettlementItemValue</t>
+  </si>
+  <si>
+    <r>
+      <t>价值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  {0:N0}</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -125,43 +225,48 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF595959"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -169,30 +274,24 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -200,15 +299,13 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -216,7 +313,6 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -224,7 +320,6 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -232,88 +327,70 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -385,19 +462,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,19 +486,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,19 +510,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -457,19 +534,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -481,19 +558,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,19 +582,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -619,7 +696,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -693,167 +770,164 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -862,16 +936,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -880,13 +948,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -894,6 +956,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="49" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1365,13 +1432,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="13.5955882352941" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.6911764705882" style="3" customWidth="1"/>
-    <col min="3" max="3" width="42.6397058823529" style="4" customWidth="1"/>
-    <col min="4" max="4" width="22.7867647058824" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.5916666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.8333333333333" style="3" customWidth="1"/>
+    <col min="3" max="3" width="42.6416666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.7833333333333" style="4" customWidth="1"/>
     <col min="5" max="5" width="28" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
@@ -1383,75 +1450,75 @@
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:4">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:4">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:4">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" customHeight="1" spans="1:4">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="19"/>
+      <c r="D5" s="14"/>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="1:4">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="19"/>
+      <c r="D6" s="14"/>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="1:4">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="19"/>
+      <c r="D7" s="14"/>
     </row>
     <row r="8" customHeight="1" spans="1:4">
       <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="2"/>
@@ -1460,7 +1527,7 @@
       <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="2"/>
@@ -1469,7 +1536,7 @@
       <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="2"/>
@@ -1478,7 +1545,7 @@
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1486,8 +1553,159 @@
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:4">
+      <c r="A13" s="1"/>
+      <c r="B13" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:4">
+      <c r="A14" s="1"/>
+      <c r="B14" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:4">
+      <c r="A15" s="1"/>
+      <c r="B15" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:4">
+      <c r="A16" s="1"/>
+      <c r="B16" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:4">
+      <c r="A17" s="1"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:4">
+      <c r="A18" s="1"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:4">
+      <c r="B19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:4">
+      <c r="A20" s="1"/>
+      <c r="B20" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:4">
+      <c r="A21" s="1"/>
+      <c r="B21" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:4">
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:4">
+      <c r="A23" s="16"/>
+      <c r="B23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:4">
+      <c r="A24" s="16"/>
+      <c r="B24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:4">
+      <c r="A25" s="16"/>
+      <c r="B25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:4">
+      <c r="A26" s="16"/>
+      <c r="B26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:4">
+      <c r="A27" s="16"/>
+      <c r="B27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:4">
+      <c r="A28" s="16"/>
+      <c r="B28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:4">
+      <c r="A29" s="16"/>
+      <c r="B29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Datas/FormatText_格式化文本.xlsx
+++ b/数据表/Datas/FormatText_格式化文本.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -170,6 +170,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">{0} </t>
     </r>
     <r>
@@ -182,9 +187,6 @@
     </r>
   </si>
   <si>
-    <t>SettlementItemName</t>
-  </si>
-  <si>
     <t>SettlementItemQuantity</t>
   </si>
   <si>
@@ -195,6 +197,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>价值</t>
     </r>
     <r>
@@ -916,7 +923,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1"/>
@@ -959,7 +966,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="49" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
@@ -1646,66 +1652,62 @@
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:4">
-      <c r="A23" s="16"/>
-      <c r="B23" s="1" t="s">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:4">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:4">
-      <c r="A24" s="16"/>
-      <c r="B24" s="1" t="s">
+    <row r="25" customHeight="1" spans="1:4">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:4">
-      <c r="A25" s="16"/>
-      <c r="B25" s="1" t="s">
+    <row r="26" customHeight="1" spans="1:4">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:4">
-      <c r="A26" s="16"/>
-      <c r="B26" s="1" t="s">
+    <row r="27" customHeight="1" spans="1:4">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:4">
-      <c r="A27" s="16"/>
-      <c r="B27" s="1" t="s">
+    <row r="28" customHeight="1" spans="1:4">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:4">
-      <c r="A28" s="16"/>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="1" t="s">
+    </row>
+    <row r="29" customHeight="1" spans="1:4">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:4">
-      <c r="A29" s="16"/>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="16" t="s">
         <v>49</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Datas/FormatText_格式化文本.xlsx
+++ b/数据表/Datas/FormatText_格式化文本.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -58,10 +58,26 @@
     <t>##</t>
   </si>
   <si>
-    <t>文本名</t>
-  </si>
-  <si>
-    <t>格式化字符串</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>文本名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>格式化字符串</t>
+    </r>
   </si>
   <si>
     <t>ATKFormatText</t>
@@ -100,81 +116,105 @@
     <t>STA   {0}</t>
   </si>
   <si>
-    <t>WarehouseCapacity</t>
-  </si>
-  <si>
-    <t>{0} ITEMS   /   {1} TOTAL UNITS</t>
-  </si>
-  <si>
-    <t>BattleBarText</t>
-  </si>
-  <si>
-    <t>{0} / {1}</t>
-  </si>
-  <si>
-    <t>RoundHUDRemainingTime</t>
-  </si>
-  <si>
-    <t>{0:00}:{1:00}</t>
-  </si>
-  <si>
-    <t>RoundHUDNorthLabel</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>RoundHUDFreeSlots</t>
-  </si>
-  <si>
-    <t>RoundHUDLootValue</t>
-  </si>
-  <si>
-    <t>{0:N0}</t>
-  </si>
-  <si>
-    <t>BackpackSafeCapacity</t>
-  </si>
-  <si>
-    <t>BackpackMemberHp</t>
-  </si>
-  <si>
-    <t>HP {0}/{1}</t>
-  </si>
-  <si>
-    <t>BackpackMemberMp</t>
-  </si>
-  <si>
-    <t>MP {0}/{1}</t>
-  </si>
-  <si>
-    <t>BackpackItemName</t>
-  </si>
-  <si>
-    <t>{0} x{1}</t>
-  </si>
-  <si>
-    <t>SettlementResult</t>
-  </si>
-  <si>
-    <t>{0}</t>
-  </si>
-  <si>
-    <t>SettlementTotalValue</t>
-  </si>
-  <si>
-    <t>SettlementElapsed</t>
-  </si>
-  <si>
-    <t>SettlementRedLootCount</t>
-  </si>
-  <si>
+    <t>LobbyFooterStatus</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>主仓库</t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
         <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
+      <t xml:space="preserve">   {0} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道具</t>
+    </r>
+  </si>
+  <si>
+    <t>WarehouseCapacity</t>
+  </si>
+  <si>
+    <t>{0} ITEMS   /   {1} TOTAL UNITS</t>
+  </si>
+  <si>
+    <t>BattleBarText</t>
+  </si>
+  <si>
+    <t>{0} / {1}</t>
+  </si>
+  <si>
+    <t>RoundHUDRemainingTime</t>
+  </si>
+  <si>
+    <t>{0:00}:{1:00}</t>
+  </si>
+  <si>
+    <t>RoundHUDNorthLabel</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>RoundHUDFreeSlots</t>
+  </si>
+  <si>
+    <t>RoundHUDLootValue</t>
+  </si>
+  <si>
+    <t>{0:N0}</t>
+  </si>
+  <si>
+    <t>BackpackSafeCapacity</t>
+  </si>
+  <si>
+    <t>BackpackMemberHp</t>
+  </si>
+  <si>
+    <t>HP {0}/{1}</t>
+  </si>
+  <si>
+    <t>BackpackMemberMp</t>
+  </si>
+  <si>
+    <t>MP {0}/{1}</t>
+  </si>
+  <si>
+    <t>BackpackItemName</t>
+  </si>
+  <si>
+    <t>{0} x{1}</t>
+  </si>
+  <si>
+    <t>SettlementResult</t>
+  </si>
+  <si>
+    <t>{0}</t>
+  </si>
+  <si>
+    <t>SettlementTotalValue</t>
+  </si>
+  <si>
+    <t>SettlementElapsed</t>
+  </si>
+  <si>
+    <t>SettlementRedLootCount</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">{0} </t>
     </r>
     <r>
@@ -261,19 +301,8 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -397,6 +426,17 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -777,19 +817,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -798,127 +847,118 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -954,19 +994,21 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1438,7 +1480,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="13.5916666666667" style="2" customWidth="1"/>
@@ -1548,166 +1590,187 @@
       <c r="D10" s="2"/>
     </row>
     <row r="11" customHeight="1" spans="1:4">
-      <c r="B11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" customHeight="1" spans="1:4">
       <c r="B12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:4">
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:4">
+      <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:4">
-      <c r="A13" s="1"/>
-      <c r="B13" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:4">
-      <c r="A14" s="1"/>
-      <c r="B14" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:4">
-      <c r="A16" s="1"/>
-      <c r="B16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:4">
-      <c r="A17" s="1"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
     </row>
     <row r="19" customHeight="1" spans="1:4">
       <c r="B19" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:4">
       <c r="A20" s="1"/>
-      <c r="B20" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="1"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="16"/>
     </row>
     <row r="21" customHeight="1" spans="1:4">
       <c r="A21" s="1"/>
       <c r="B21" s="15" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D21" s="1"/>
     </row>
     <row r="22" customHeight="1" spans="1:4">
-      <c r="B22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>39</v>
-      </c>
+      <c r="A22" s="1"/>
+      <c r="B22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="1"/>
     </row>
     <row r="23" customHeight="1" spans="1:4">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
+      <c r="B23" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="1"/>
     </row>
     <row r="24" customHeight="1" spans="1:4">
       <c r="A24" s="1"/>
-      <c r="B24" s="1" t="s">
-        <v>40</v>
+      <c r="B24" s="15" t="s">
+        <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>41</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D24" s="1"/>
     </row>
     <row r="25" customHeight="1" spans="1:4">
       <c r="A25" s="1"/>
-      <c r="B25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
     </row>
     <row r="26" customHeight="1" spans="1:4">
       <c r="A26" s="1"/>
-      <c r="B26" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="1" t="s">
+      <c r="B26" s="15"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:4">
+      <c r="B27" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:4">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:4">
       <c r="A28" s="1"/>
-      <c r="B28" s="1" t="s">
-        <v>46</v>
+      <c r="B28" s="15" t="s">
+        <v>36</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>47</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D28" s="1"/>
     </row>
     <row r="29" customHeight="1" spans="1:4">
       <c r="A29" s="1"/>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:4">
+      <c r="B30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:4">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:4">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:3">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:3">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:3">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:3">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C36" s="1" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:3">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Datas/FormatText_格式化文本.xlsx
+++ b/数据表/Datas/FormatText_格式化文本.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -151,6 +151,12 @@
     <t>{0} ITEMS   /   {1} TOTAL UNITS</t>
   </si>
   <si>
+    <t>SquadMemberText</t>
+  </si>
+  <si>
+    <t>{0} / {1} Selected</t>
+  </si>
+  <si>
     <t>BattleBarText</t>
   </si>
   <si>
@@ -215,6 +221,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">{0} </t>
     </r>
     <r>
@@ -1612,12 +1623,20 @@
         <v>25</v>
       </c>
     </row>
+    <row r="17" customHeight="1" spans="1:4">
+      <c r="B17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="19" customHeight="1" spans="1:4">
       <c r="B19" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:4">
@@ -1629,40 +1648,40 @@
     <row r="21" customHeight="1" spans="1:4">
       <c r="A21" s="1"/>
       <c r="B21" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D21" s="1"/>
     </row>
     <row r="22" customHeight="1" spans="1:4">
       <c r="A22" s="1"/>
       <c r="B22" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D22" s="1"/>
     </row>
     <row r="23" customHeight="1" spans="1:4">
       <c r="A23" s="1"/>
       <c r="B23" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D23" s="1"/>
     </row>
     <row r="24" customHeight="1" spans="1:4">
       <c r="A24" s="1"/>
       <c r="B24" s="15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D24" s="1"/>
     </row>
@@ -1680,38 +1699,38 @@
     </row>
     <row r="27" customHeight="1" spans="1:4">
       <c r="B27" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:4">
       <c r="A28" s="1"/>
       <c r="B28" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D28" s="1"/>
     </row>
     <row r="29" customHeight="1" spans="1:4">
       <c r="A29" s="1"/>
       <c r="B29" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D29" s="1"/>
     </row>
     <row r="30" customHeight="1" spans="1:4">
       <c r="B30" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:4">
@@ -1722,55 +1741,55 @@
     <row r="32" customHeight="1" spans="1:4">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:3">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:3">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:3">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:3">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
